--- a/endpoint_excels/iss__engines__engine__markets__market__boardgroups__boardgroup__securities__security__candleborders.xlsx
+++ b/endpoint_excels/iss__engines__engine__markets__market__boardgroups__boardgroup__securities__security__candleborders.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,16 +28,26 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -51,14 +61,31 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -134,6 +161,21 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TBL_01_iss__engines__engi" displayName="TBL_01_iss__engines__engi" ref="A1:F26" headerRowCount="1">
+  <autoFilter ref="A1:F26"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="SECID"/>
+    <tableColumn id="2" name="REQUEST_URL"/>
+    <tableColumn id="3" name="begin"/>
+    <tableColumn id="4" name="end"/>
+    <tableColumn id="5" name="interval"/>
+    <tableColumn id="6" name="board_group_id"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -427,8 +469,16 @@
   </sheetPr>
   <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SECID</t>
@@ -461,706 +511,709 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SU26238RMFS4</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SU26238RMFS4</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/SU26238RMFS4/candleborders.json</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2021-06-23 14:44:00</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 18:59:59</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SU26238RMFS4</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/SU26238RMFS4/candleborders.json</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2021-04-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SU26238RMFS4</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/SU26238RMFS4/candleborders.json</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2021-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SU26238RMFS4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/SU26238RMFS4/candleborders.json</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2021-06-23 14:40:00</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 18:15:56</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SU26238RMFS4</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/SU26238RMFS4/candleborders.json</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2021-06-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 18:15:57</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SU26238RMFS4</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/SU26238RMFS4/candleborders.json</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2021-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SU26238RMFS4</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/SU26238RMFS4/candleborders.json</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2021-06-23 14:00:00</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 18:15:56</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SU26238RMFS4</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/123/securities/SU26238RMFS4/candleborders.json</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>2021-04-01 00:00:00</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>2023-01-01 00:00:00</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E9" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F9" s="2" t="n">
         <v>123</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SU26238RMFS4</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SU26238RMFS4</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/123/securities/SU26238RMFS4/candleborders.json</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>2021-06-21 00:00:00</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>2023-03-27 00:00:00</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E10" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F10" s="2" t="n">
         <v>123</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>SU26238RMFS4</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>SU26238RMFS4</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/123/securities/SU26238RMFS4/candleborders.json</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>2021-06-23 00:00:00</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>2023-03-29 00:00:00</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E11" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F11" s="2" t="n">
         <v>123</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SU26238RMFS4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SU26238RMFS4</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/123/securities/SU26238RMFS4/candleborders.json</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>2021-06-01 00:00:00</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>2023-03-01 00:00:00</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E12" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F12" s="2" t="n">
         <v>123</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SU26238RMFS4</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SU26238RMFS4</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/257/securities/SU26238RMFS4/candleborders.json</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>2023-04-26 16:34:00</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>2025-09-24 16:24:00</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F13" s="2" t="n">
         <v>257</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SU26238RMFS4</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>SU26238RMFS4</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/257/securities/SU26238RMFS4/candleborders.json</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>2023-04-01 00:00:00</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>2025-07-01 00:00:00</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E14" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F14" s="2" t="n">
         <v>257</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SU26238RMFS4</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SU26238RMFS4</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/257/securities/SU26238RMFS4/candleborders.json</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>2023-04-24 00:00:00</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>2025-09-22 00:00:00</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E15" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F15" s="2" t="n">
         <v>257</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SU26238RMFS4</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SU26238RMFS4</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/257/securities/SU26238RMFS4/candleborders.json</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>2023-04-26 16:30:00</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>2025-09-24 16:20:00</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E16" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F16" s="2" t="n">
         <v>257</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SU26238RMFS4</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>SU26238RMFS4</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/257/securities/SU26238RMFS4/candleborders.json</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>2023-04-26 00:00:00</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>2025-09-24 00:00:00</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E17" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F17" s="2" t="n">
         <v>257</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SU26238RMFS4</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>SU26238RMFS4</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/257/securities/SU26238RMFS4/candleborders.json</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>2023-04-01 00:00:00</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>2025-09-01 00:00:00</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E18" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F18" s="2" t="n">
         <v>257</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>SU26238RMFS4</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>SU26238RMFS4</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/257/securities/SU26238RMFS4/candleborders.json</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>2023-04-26 16:00:00</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>2025-09-24 16:00:00</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E19" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F19" s="2" t="n">
         <v>257</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>SU26238RMFS4</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/SU26238RMFS4/candleborders.json</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2021-06-23 14:44:00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-02-16 18:59:59</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>RU000A1041Q0</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/RU000A1041Q0/candleborders.json</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2021-11-18 16:09:00</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 13:59:59</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F13" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>SU26238RMFS4</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/SU26238RMFS4/candleborders.json</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2021-04-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="F20" s="2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>RU000A1041Q0</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/RU000A1041Q0/candleborders.json</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>2021-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>2026-03-31 00:00:00</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E21" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F14" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>SU26238RMFS4</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/SU26238RMFS4/candleborders.json</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2021-06-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="F21" s="2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>RU000A1041Q0</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/RU000A1041Q0/candleborders.json</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2021-11-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>2026-02-22 00:00:00</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E22" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="F15" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>SU26238RMFS4</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/SU26238RMFS4/candleborders.json</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2021-06-23 14:40:00</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-02-16 18:15:56</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
+      <c r="F22" s="2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>RU000A1041Q0</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/RU000A1041Q0/candleborders.json</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2021-11-18 16:00:00</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 13:41:05</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F16" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>SU26238RMFS4</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/SU26238RMFS4/candleborders.json</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2021-06-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-02-16 18:15:57</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
+      <c r="F23" s="2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>RU000A1041Q0</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/RU000A1041Q0/candleborders.json</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2021-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 18:16:16</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="F17" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>SU26238RMFS4</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/SU26238RMFS4/candleborders.json</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2021-06-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="F24" s="2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>RU000A1041Q0</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/RU000A1041Q0/candleborders.json</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>2021-11-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>2026-02-28 00:00:00</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E25" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="F18" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>SU26238RMFS4</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/SU26238RMFS4/candleborders.json</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2021-06-23 14:00:00</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-02-16 18:15:56</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
+      <c r="F25" s="2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>RU000A1041Q0</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/RU000A1041Q0/candleborders.json</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>2021-11-18 16:00:00</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 13:41:05</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="F19" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>RU000A1041Q0</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/RU000A1041Q0/candleborders.json</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2021-11-18 16:09:00</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-02-16 13:59:59</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>RU000A1041Q0</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/RU000A1041Q0/candleborders.json</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2021-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-03-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>RU000A1041Q0</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/RU000A1041Q0/candleborders.json</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2021-11-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-02-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>7</v>
-      </c>
-      <c r="F22" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>RU000A1041Q0</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/RU000A1041Q0/candleborders.json</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2021-11-18 16:00:00</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-02-16 13:41:05</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>10</v>
-      </c>
-      <c r="F23" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>RU000A1041Q0</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/RU000A1041Q0/candleborders.json</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2021-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-02-16 18:16:16</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>24</v>
-      </c>
-      <c r="F24" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>RU000A1041Q0</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/RU000A1041Q0/candleborders.json</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2021-11-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-02-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>31</v>
-      </c>
-      <c r="F25" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>RU000A1041Q0</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boardgroups/58/securities/RU000A1041Q0/candleborders.json</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2021-11-18 16:00:00</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-02-16 13:41:05</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>60</v>
-      </c>
-      <c r="F26" t="n">
+      <c r="F26" s="2" t="n">
         <v>58</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>